--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.60351432467814</v>
+        <v>6.435571077760198</v>
       </c>
       <c r="D2" t="n">
-        <v>39.58254294065583</v>
+        <v>6.432163227856572</v>
       </c>
       <c r="E2" t="n">
-        <v>3.136730563005444</v>
+        <v>0.5097187164883846</v>
       </c>
       <c r="F2" t="n">
-        <v>8.295764350836691</v>
+        <v>1.348061707010962</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.02365323212731</v>
+        <v>7.478843650220688</v>
       </c>
       <c r="D3" t="n">
-        <v>46.04891145587065</v>
+        <v>7.482948111578981</v>
       </c>
       <c r="E3" t="n">
-        <v>3.136730563005444</v>
+        <v>0.5097187164883846</v>
       </c>
       <c r="F3" t="n">
-        <v>8.295764350836691</v>
+        <v>1.348061707010962</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.52220749068912</v>
+        <v>7.559858717236982</v>
       </c>
       <c r="D4" t="n">
-        <v>23.28750149102399</v>
+        <v>3.784218992291399</v>
       </c>
       <c r="E4" t="n">
-        <v>3.136730563005444</v>
+        <v>0.5097187164883846</v>
       </c>
       <c r="F4" t="n">
-        <v>8.295764350836691</v>
+        <v>1.348061707010962</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.62339169951368</v>
+        <v>7.738801151170974</v>
       </c>
       <c r="D5" t="n">
-        <v>35.87819986697276</v>
+        <v>5.830207478383074</v>
       </c>
       <c r="E5" t="n">
-        <v>3.136730563005444</v>
+        <v>0.5097187164883846</v>
       </c>
       <c r="F5" t="n">
-        <v>8.295764350836691</v>
+        <v>1.348061707010962</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
